--- a/docs/package/05_Delivery/Upload_Templates/TFS_Accounts_Upload_Template.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/TFS_Accounts_Upload_Template.xlsx
@@ -378,7 +378,7 @@
     <t xml:space="preserve">Upload on</t>
   </si>
   <si>
-    <t xml:space="preserve">Operations &gt; Sales &amp; Marketing &gt; Prospects &gt; Bulk Upload &gt; TFS accounts</t>
+    <t xml:space="preserve">Sales &amp; Placement &gt; Prospects &gt; Bulk Upload &gt; TFS accounts</t>
   </si>
   <si>
     <t xml:space="preserve">File types</t>
